--- a/Document/100_DUYD画面仕様.xlsx
+++ b/Document/100_DUYD画面仕様.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3354EEF3-5F6D-4A01-8221-25CDC5D26175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7FB8F4-01E2-4D9C-837C-5A3B69528118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="188">
   <si>
     <t>更新日</t>
   </si>
@@ -1752,6 +1752,14 @@
     <rPh sb="19" eb="21">
       <t>キサイ</t>
     </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>pキー</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>tキー</t>
     <phoneticPr fontId="10"/>
   </si>
 </sst>
@@ -1996,7 +2004,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2055,6 +2063,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4443,315 +4452,320 @@
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="角丸四角形 25">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="11" name="グループ化 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BD3F407-A970-470D-9AE9-2EF72332E1F4}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DAF98D5F-CC67-4723-A912-B46D3C3878D1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93470CB8-B4CB-4722-94AC-B7607426AA99}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4152900" y="7305675"/>
-          <a:ext cx="2295525" cy="714375"/>
+          <a:off x="4131945" y="8151495"/>
+          <a:ext cx="2268855" cy="800100"/>
+          <a:chOff x="4131945" y="8151495"/>
+          <a:chExt cx="2268855" cy="800100"/>
         </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="26" name="角丸四角形 25">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BD3F407-A970-470D-9AE9-2EF72332E1F4}"/>
+              </a:ext>
+              <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+                <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DAF98D5F-CC67-4723-A912-B46D3C3878D1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4131945" y="8151495"/>
+            <a:ext cx="2268855" cy="714375"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
             <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle>
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>DUYD</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="テキスト ボックス 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ADCBA25-CA69-4B89-A0BA-ED545A1A7E48}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5BD3F407-A970-470D-9AE9-2EF72332E1F4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4619625" y="7781925"/>
-          <a:ext cx="1419225" cy="323850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>DUYD</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="27" name="テキスト ボックス 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ADCBA25-CA69-4B89-A0BA-ED545A1A7E48}"/>
+              </a:ext>
+              <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+                <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5BD3F407-A970-470D-9AE9-2EF72332E1F4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4592955" y="8627745"/>
+            <a:ext cx="1403985" cy="323850"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
-            <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle>
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>～</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-lt"/>
-              <a:cs typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>Dig until you die</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>～</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle>
+            <a:lvl1pPr marL="0" indent="0">
+              <a:defRPr sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" indent="0">
+              <a:defRPr sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" indent="0">
+              <a:defRPr sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" indent="0">
+              <a:defRPr sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" indent="0">
+              <a:defRPr sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" indent="0">
+              <a:defRPr sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" indent="0">
+              <a:defRPr sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" indent="0">
+              <a:defRPr sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" indent="0">
+              <a:defRPr sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr marL="0" indent="0" algn="l"/>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>～</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100">
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Dig until you die</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>～</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -5085,7 +5099,7 @@
               <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>索探開始探索</a:t>
+            <a:t>索探開始</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -8613,6 +8627,106 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="直線コネクタ 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{457D3CDE-6CA3-4B0D-B561-3C4C2827EBFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3771900" y="11582400"/>
+          <a:ext cx="1424940" cy="7620"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="直線コネクタ 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAEF4BE0-F014-462B-A466-AA06E6EE803B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3512820" y="17312640"/>
+          <a:ext cx="1424940" cy="7620"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -30579,7 +30693,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF07837F-3729-4EA6-A844-0445594FBC74}">
-  <dimension ref="A1:N143"/>
+  <dimension ref="A1:Q143"/>
   <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -30695,22 +30809,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="6:14" ht="18" customHeight="1">
+    <row r="65" spans="6:17" ht="18" customHeight="1">
       <c r="G65" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="6:14" ht="18.600000000000001" customHeight="1">
+    <row r="69" spans="6:17" ht="18.600000000000001" customHeight="1">
       <c r="L69" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="6:14" ht="17.399999999999999" customHeight="1">
+    <row r="70" spans="6:17" ht="12" customHeight="1">
+      <c r="Q70" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="71" spans="6:17" ht="17.399999999999999" customHeight="1">
       <c r="H71" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="6:14" ht="18" customHeight="1">
+    <row r="73" spans="6:17" ht="18" customHeight="1">
       <c r="F73" t="s">
         <v>13</v>
       </c>
@@ -30721,17 +30840,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="6:14" ht="17.399999999999999" customHeight="1">
+    <row r="75" spans="6:17" ht="17.399999999999999" customHeight="1">
       <c r="G75" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="6:14" ht="15" customHeight="1">
+    <row r="77" spans="6:17" ht="15" customHeight="1">
       <c r="F77" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="6:14" ht="16.2" customHeight="1">
+    <row r="79" spans="6:17" ht="16.2" customHeight="1">
       <c r="G79" t="s">
         <v>26</v>
       </c>
@@ -30763,22 +30882,27 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="6:14" ht="13.8" customHeight="1">
+    <row r="97" spans="6:15" ht="13.8" customHeight="1">
       <c r="F97" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="6:14" ht="17.399999999999999" customHeight="1">
+    <row r="102" spans="6:15" ht="17.399999999999999" customHeight="1">
       <c r="J102" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="6:14" ht="17.399999999999999" customHeight="1">
+    <row r="103" spans="6:15" ht="12" customHeight="1">
+      <c r="O103" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="104" spans="6:15" ht="17.399999999999999" customHeight="1">
       <c r="G104" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="6:14" ht="17.399999999999999" customHeight="1">
+    <row r="106" spans="6:15" ht="17.399999999999999" customHeight="1">
       <c r="F106" t="s">
         <v>13</v>
       </c>
@@ -30789,12 +30913,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="6:14" ht="16.8" customHeight="1">
+    <row r="108" spans="6:15" ht="16.8" customHeight="1">
       <c r="G108" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="6:14" ht="16.8" customHeight="1">
+    <row r="111" spans="6:15" ht="16.8" customHeight="1">
       <c r="F111" t="s">
         <v>17</v>
       </c>
@@ -31161,11 +31285,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="140" spans="2:4" s="6" customFormat="1" ht="16.05" customHeight="1">
-      <c r="B140" s="41"/>
-      <c r="D140" s="42" t="s">
-        <v>113</v>
-      </c>
+    <row r="140" spans="2:4" s="22" customFormat="1" ht="16.05" customHeight="1">
+      <c r="B140" s="45"/>
+      <c r="D140" s="46"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10"/>

--- a/Document/100_DUYD画面仕様.xlsx
+++ b/Document/100_DUYD画面仕様.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7FB8F4-01E2-4D9C-837C-5A3B69528118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFFB293-2191-460A-9C98-7927D543928A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1343" yWindow="473" windowWidth="13372" windowHeight="11152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="190">
   <si>
     <t>更新日</t>
   </si>
@@ -1760,6 +1760,23 @@
   </si>
   <si>
     <t>tキー</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>これもテロップ形式で説明</t>
+    <rPh sb="7" eb="9">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>説明様式変更</t>
+    <rPh sb="0" eb="6">
+      <t>セツメイヨウシキヘンコウ</t>
+    </rPh>
     <phoneticPr fontId="10"/>
   </si>
 </sst>
@@ -2004,7 +2021,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2064,6 +2081,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4468,8 +4488,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4131945" y="8151495"/>
-          <a:ext cx="2268855" cy="800100"/>
+          <a:off x="4152900" y="8110538"/>
+          <a:ext cx="2295525" cy="800100"/>
           <a:chOff x="4131945" y="8151495"/>
           <a:chExt cx="2268855" cy="800100"/>
         </a:xfrm>
@@ -8760,8 +8780,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1767841" y="2438400"/>
-          <a:ext cx="4358640" cy="1386840"/>
+          <a:off x="2079343" y="2453538"/>
+          <a:ext cx="4311763" cy="1398984"/>
           <a:chOff x="1766889" y="1657350"/>
           <a:chExt cx="4333875" cy="1400175"/>
         </a:xfrm>
@@ -9232,8 +9252,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7970520" y="2438400"/>
-          <a:ext cx="4358640" cy="1386840"/>
+          <a:off x="8215313" y="2453538"/>
+          <a:ext cx="4311763" cy="1398984"/>
           <a:chOff x="1766889" y="1657350"/>
           <a:chExt cx="4333875" cy="1400175"/>
         </a:xfrm>
@@ -10834,8 +10854,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1945006" y="6207442"/>
-          <a:ext cx="4358640" cy="1386840"/>
+          <a:off x="2254705" y="6255543"/>
+          <a:ext cx="4311763" cy="1398985"/>
           <a:chOff x="1766889" y="1657350"/>
           <a:chExt cx="4333875" cy="1400175"/>
         </a:xfrm>
@@ -12303,8 +12323,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2270760" y="14127480"/>
-          <a:ext cx="4358640" cy="1386840"/>
+          <a:off x="2576853" y="14244978"/>
+          <a:ext cx="4311763" cy="1398985"/>
           <a:chOff x="1766889" y="1657350"/>
           <a:chExt cx="4333875" cy="1400175"/>
         </a:xfrm>
@@ -12967,8 +12987,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2103120" y="1760116"/>
-          <a:ext cx="3822249" cy="594464"/>
+          <a:off x="2411016" y="1768315"/>
+          <a:ext cx="3782584" cy="599668"/>
           <a:chOff x="8767763" y="5857875"/>
           <a:chExt cx="3801294" cy="600179"/>
         </a:xfrm>
@@ -13793,8 +13813,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8381181" y="1807741"/>
-          <a:ext cx="3823201" cy="594464"/>
+          <a:off x="8622368" y="1815940"/>
+          <a:ext cx="3781733" cy="599668"/>
           <a:chOff x="8767763" y="5857875"/>
           <a:chExt cx="3801294" cy="600179"/>
         </a:xfrm>
@@ -14887,8 +14907,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1935480" y="20863560"/>
-          <a:ext cx="3822249" cy="594464"/>
+          <a:off x="2245179" y="21040045"/>
+          <a:ext cx="3782584" cy="599669"/>
           <a:chOff x="8767763" y="5857875"/>
           <a:chExt cx="3801294" cy="600179"/>
         </a:xfrm>
@@ -17418,8 +17438,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7025640" y="1645920"/>
-          <a:ext cx="3848100" cy="2598420"/>
+          <a:off x="7086600" y="1643063"/>
+          <a:ext cx="3895725" cy="2598420"/>
           <a:chOff x="2080260" y="1455420"/>
           <a:chExt cx="3848100" cy="2103120"/>
         </a:xfrm>
@@ -19965,8 +19985,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6553200" y="9715500"/>
-          <a:ext cx="3848100" cy="2598420"/>
+          <a:off x="6610350" y="9712643"/>
+          <a:ext cx="3893820" cy="2598420"/>
           <a:chOff x="2080260" y="1455420"/>
           <a:chExt cx="3848100" cy="2103120"/>
         </a:xfrm>
@@ -22502,8 +22522,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2545080" y="19857720"/>
-          <a:ext cx="3848100" cy="2598420"/>
+          <a:off x="2552700" y="19854863"/>
+          <a:ext cx="3895725" cy="2598420"/>
           <a:chOff x="2080260" y="1455420"/>
           <a:chExt cx="3848100" cy="2103120"/>
         </a:xfrm>
@@ -24031,8 +24051,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2636520" y="26868120"/>
-          <a:ext cx="3848100" cy="2598420"/>
+          <a:off x="2646045" y="26865263"/>
+          <a:ext cx="3893820" cy="2598420"/>
           <a:chOff x="2080260" y="1455420"/>
           <a:chExt cx="3848100" cy="2103120"/>
         </a:xfrm>
@@ -26197,8 +26217,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2270760" y="3627120"/>
-          <a:ext cx="1844040" cy="1211580"/>
+          <a:off x="2266950" y="3657600"/>
+          <a:ext cx="1833563" cy="1223010"/>
           <a:chOff x="2270760" y="3627120"/>
           <a:chExt cx="1844040" cy="1211580"/>
         </a:xfrm>
@@ -26452,8 +26472,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5676900" y="3649980"/>
-          <a:ext cx="1844040" cy="1211580"/>
+          <a:off x="5654040" y="3680460"/>
+          <a:ext cx="1833563" cy="1223010"/>
           <a:chOff x="2270760" y="3627120"/>
           <a:chExt cx="1844040" cy="1211580"/>
         </a:xfrm>
@@ -28063,8 +28083,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5600700" y="2552700"/>
-          <a:ext cx="1844040" cy="1211580"/>
+          <a:off x="5578793" y="2571750"/>
+          <a:ext cx="1833562" cy="1223010"/>
           <a:chOff x="2270760" y="3627120"/>
           <a:chExt cx="1844040" cy="1211580"/>
         </a:xfrm>
@@ -28318,8 +28338,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2316480" y="2567940"/>
-          <a:ext cx="1844040" cy="1211580"/>
+          <a:off x="2312670" y="2586990"/>
+          <a:ext cx="1833563" cy="1223010"/>
           <a:chOff x="2270760" y="3627120"/>
           <a:chExt cx="1844040" cy="1211580"/>
         </a:xfrm>
@@ -28573,8 +28593,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2331720" y="9311640"/>
-          <a:ext cx="1844040" cy="1211580"/>
+          <a:off x="2327910" y="9395460"/>
+          <a:ext cx="1833563" cy="1223010"/>
           <a:chOff x="2270760" y="3627120"/>
           <a:chExt cx="1844040" cy="1211580"/>
         </a:xfrm>
@@ -28828,8 +28848,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5730240" y="9319260"/>
-          <a:ext cx="1844040" cy="1211580"/>
+          <a:off x="5707380" y="9403080"/>
+          <a:ext cx="1833563" cy="1223010"/>
           <a:chOff x="2270760" y="3627120"/>
           <a:chExt cx="1844040" cy="1211580"/>
         </a:xfrm>
@@ -30584,18 +30604,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:G9"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="13.05" customHeight="1"/>
+  <dimension ref="B1:G10"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="13.05" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="2.09765625" style="20"/>
+    <col min="1" max="3" width="2.125" style="20"/>
     <col min="4" max="4" width="11.5" style="20" customWidth="1"/>
-    <col min="5" max="5" width="8.09765625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="20.8984375" style="20" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" style="20" customWidth="1"/>
-    <col min="8" max="16384" width="2.09765625" style="20"/>
+    <col min="5" max="5" width="8.125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="20.875" style="20" customWidth="1"/>
+    <col min="7" max="7" width="11.1875" style="20" customWidth="1"/>
+    <col min="8" max="16384" width="2.125" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" s="19" customFormat="1" ht="26.4">
+    <row r="1" spans="2:7" s="19" customFormat="1" ht="25.9">
       <c r="B1" s="18" t="s">
         <v>41</v>
       </c>
@@ -30684,6 +30704,20 @@
         <v>48</v>
       </c>
     </row>
+    <row r="10" spans="2:7" ht="14.65" customHeight="1">
+      <c r="D10" s="48">
+        <v>46091</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="49" t="s">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30694,7 +30728,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF07837F-3729-4EA6-A844-0445594FBC74}">
   <dimension ref="A1:Q143"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16.5" style="3" customWidth="1"/>
@@ -30717,7 +30751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.4" customHeight="1">
+    <row r="5" spans="1:5" ht="14.45" customHeight="1">
       <c r="E5" t="s">
         <v>4</v>
       </c>
@@ -30743,7 +30777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="16.2" customHeight="1">
+    <row r="29" spans="2:6" ht="16.25" customHeight="1">
       <c r="F29" t="s">
         <v>9</v>
       </c>
@@ -30753,7 +30787,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="2:6" s="12" customFormat="1" ht="16.2" customHeight="1">
+    <row r="32" spans="2:6" s="12" customFormat="1" ht="16.25" customHeight="1">
       <c r="B32" s="11"/>
       <c r="C32"/>
       <c r="E32" s="12" t="s">
@@ -30765,7 +30799,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="6:14" ht="16.2" customHeight="1">
+    <row r="36" spans="6:14" ht="16.25" customHeight="1">
       <c r="F36" t="s">
         <v>13</v>
       </c>
@@ -30787,7 +30821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="6:14" ht="16.2" customHeight="1">
+    <row r="42" spans="6:14" ht="16.25" customHeight="1">
       <c r="G42" t="s">
         <v>18</v>
       </c>
@@ -30824,7 +30858,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="71" spans="6:17" ht="17.399999999999999" customHeight="1">
+    <row r="71" spans="6:17" ht="17.45" customHeight="1">
       <c r="H71" t="s">
         <v>24</v>
       </c>
@@ -30840,7 +30874,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="6:17" ht="17.399999999999999" customHeight="1">
+    <row r="75" spans="6:17" ht="17.45" customHeight="1">
       <c r="G75" s="13" t="s">
         <v>16</v>
       </c>
@@ -30850,7 +30884,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="6:17" ht="16.2" customHeight="1">
+    <row r="79" spans="6:17" ht="16.25" customHeight="1">
       <c r="G79" t="s">
         <v>26</v>
       </c>
@@ -30870,7 +30904,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" spans="2:9" s="12" customFormat="1" ht="17.399999999999999" customHeight="1">
+    <row r="93" spans="2:9" s="12" customFormat="1" ht="17.45" customHeight="1">
       <c r="B93" s="11"/>
       <c r="C93"/>
       <c r="E93" s="12" t="s">
@@ -30887,7 +30921,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="6:15" ht="17.399999999999999" customHeight="1">
+    <row r="102" spans="6:15" ht="17.45" customHeight="1">
       <c r="J102" s="14" t="s">
         <v>23</v>
       </c>
@@ -30897,12 +30931,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="104" spans="6:15" ht="17.399999999999999" customHeight="1">
+    <row r="104" spans="6:15" ht="17.45" customHeight="1">
       <c r="G104" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="6:15" ht="17.399999999999999" customHeight="1">
+    <row r="106" spans="6:15" ht="17.45" customHeight="1">
       <c r="F106" t="s">
         <v>13</v>
       </c>
@@ -30943,7 +30977,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="2:7" s="12" customFormat="1" ht="17.399999999999999" customHeight="1">
+    <row r="131" spans="2:7" s="12" customFormat="1" ht="17.45" customHeight="1">
       <c r="B131" s="11"/>
       <c r="C131"/>
       <c r="E131" s="12" t="s">
@@ -30955,7 +30989,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="134" spans="2:7" ht="10.199999999999999" customHeight="1"/>
+    <row r="134" spans="2:7" ht="10.25" customHeight="1"/>
     <row r="135" spans="2:7" ht="16.8" customHeight="1">
       <c r="F135" t="s">
         <v>35</v>
@@ -30976,7 +31010,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="143" spans="2:7" s="6" customFormat="1" ht="16.2" customHeight="1">
+    <row r="143" spans="2:7" s="6" customFormat="1" ht="16.25" customHeight="1">
       <c r="B143" s="7"/>
       <c r="D143" s="8" t="s">
         <v>38</v>
@@ -30991,14 +31025,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D60A44-A4CA-4D99-9555-5176D472C29F}">
-  <dimension ref="A1:J140"/>
-  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="16.05" customHeight="1"/>
+  <dimension ref="A1:S140"/>
+  <sheetFormatPr defaultColWidth="2.1875" defaultRowHeight="16.05" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="12" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="34" customFormat="1" ht="20.399999999999999" customHeight="1">
+    <row r="1" spans="1:5" s="34" customFormat="1" ht="20.45" customHeight="1">
       <c r="A1" s="31" t="s">
         <v>114</v>
       </c>
@@ -31112,55 +31146,64 @@
         <v>169</v>
       </c>
     </row>
-    <row r="49" spans="4:6" ht="16.05" customHeight="1">
+    <row r="49" spans="1:19" ht="16.05" customHeight="1">
       <c r="D49" s="23"/>
       <c r="E49" s="23" t="s">
         <v>158</v>
       </c>
       <c r="F49" s="23"/>
     </row>
-    <row r="51" spans="4:6" ht="16.05" customHeight="1">
+    <row r="51" spans="1:19" ht="16.05" customHeight="1">
       <c r="E51" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="53" spans="4:6" ht="16.05" customHeight="1">
+    <row r="53" spans="1:19" ht="16.05" customHeight="1">
       <c r="F53" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="4:6" ht="16.05" customHeight="1">
+    <row r="55" spans="1:19" ht="16.05" customHeight="1">
       <c r="D55" s="23"/>
       <c r="E55" s="23" t="s">
         <v>161</v>
       </c>
       <c r="F55" s="23"/>
     </row>
-    <row r="57" spans="4:6" ht="16.05" customHeight="1">
+    <row r="57" spans="1:19" ht="16.05" customHeight="1">
       <c r="E57" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="4:6" ht="16.05" customHeight="1">
+    <row r="58" spans="1:19" ht="16.05" customHeight="1">
       <c r="F58" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="60" spans="4:6" ht="16.05" customHeight="1">
+    <row r="60" spans="1:19" ht="16.05" customHeight="1">
       <c r="D60" s="23"/>
       <c r="E60" s="23" t="s">
         <v>164</v>
       </c>
       <c r="F60" s="23"/>
     </row>
-    <row r="62" spans="4:6" ht="16.05" customHeight="1">
+    <row r="62" spans="1:19" ht="16.05" customHeight="1">
       <c r="E62" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="4:6" ht="16.05" customHeight="1">
+    <row r="63" spans="1:19" ht="16.05" customHeight="1">
+      <c r="A63" s="47">
+        <v>46091</v>
+      </c>
+      <c r="B63" s="29" t="s">
+        <v>189</v>
+      </c>
       <c r="F63" t="s">
         <v>166</v>
+      </c>
+      <c r="S63" s="13" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="4:8" ht="16.05" customHeight="1">
@@ -31300,7 +31343,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{008EA669-9892-4983-8339-6D8C60A35D66}">
   <dimension ref="A1:U158"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="11" style="3" customWidth="1"/>
@@ -31744,13 +31787,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B963E13-58BB-4108-B888-103133C66C85}">
   <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="16.05" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="2.1875" defaultRowHeight="16.05" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="12" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="34" customFormat="1" ht="20.399999999999999" customHeight="1">
+    <row r="1" spans="1:5" s="34" customFormat="1" ht="20.45" customHeight="1">
       <c r="A1" s="31" t="s">
         <v>114</v>
       </c>
@@ -31842,13 +31885,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F3175F1-FB4D-4C54-BFB0-C9A1185C8A4E}">
   <dimension ref="A1:I74"/>
-  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="16.05" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="2.1875" defaultRowHeight="16.05" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="12" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="34" customFormat="1" ht="20.399999999999999" customHeight="1">
+    <row r="1" spans="1:5" s="34" customFormat="1" ht="20.45" customHeight="1">
       <c r="A1" s="31" t="s">
         <v>114</v>
       </c>

--- a/Document/100_DUYD画面仕様.xlsx
+++ b/Document/100_DUYD画面仕様.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFFB293-2191-460A-9C98-7927D543928A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857F669E-AE85-4F23-8DC6-22116E48AB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1343" yWindow="473" windowWidth="13372" windowHeight="11152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1343" yWindow="473" windowWidth="13372" windowHeight="11152" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="1" r:id="rId1"/>

--- a/Document/100_DUYD画面仕様.xlsx
+++ b/Document/100_DUYD画面仕様.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DUYD\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857F669E-AE85-4F23-8DC6-22116E48AB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB8F408-34ED-4120-8C11-47130F33104F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1343" yWindow="473" windowWidth="13372" windowHeight="11152" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="1" r:id="rId1"/>
